--- a/data/美股_持倉季度追蹤.xlsx
+++ b/data/美股_持倉季度追蹤.xlsx
@@ -1112,7 +1112,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-58%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-48%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/data/美股_持倉季度追蹤.xlsx
+++ b/data/美股_持倉季度追蹤.xlsx
@@ -711,16 +711,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+16%</t>
+          <t>+22%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1816%</t>
+          <t>+33%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>19.07</v>
+        <v>21.26</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
@@ -803,16 +803,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+22%</t>
+          <t>+24%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+82%</t>
+          <t>+294%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>62.45</v>
+        <v>61.65</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+6%</t>
+          <t>+7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+41%</t>
+          <t>+36%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1061,16 +1061,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+16%</t>
+          <t>+26%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+8%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>21.08</v>
+        <v>16.83</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
